--- a/sheets/조재수대금교본/검수/고姑 본청.xlsx
+++ b/sheets/조재수대금교본/검수/고姑 본청.xlsx
@@ -3239,7 +3239,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌ㄱ</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -3252,13 +3252,13 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑∽</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
       <c r="R3" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑∽</t>
+          <t xml:space="preserve">姑</t>
         </is>
       </c>
       <c r="S3" s="24"/>
@@ -3271,25 +3271,13 @@
       <c r="E4" s="25"/>
       <c r="F4" s="21"/>
       <c r="G4" s="25"/>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ʒ</t>
-        </is>
-      </c>
+      <c r="H4" s="21"/>
       <c r="I4" s="25"/>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ʒ</t>
-        </is>
-      </c>
+      <c r="J4" s="21"/>
       <c r="K4" s="25"/>
       <c r="L4" s="21"/>
       <c r="M4" s="25"/>
-      <c r="N4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ʒ</t>
-        </is>
-      </c>
+      <c r="N4" s="21"/>
       <c r="O4" s="25"/>
       <c r="P4" s="21"/>
       <c r="Q4" s="25"/>
@@ -3301,30 +3289,27 @@
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-‹</t>
+          <t xml:space="preserve">㳞</t>
         </is>
       </c>
       <c r="E5" s="26"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="G5" s="26"/>
       <c r="H5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲?</t>
+仲</t>
         </is>
       </c>
       <c r="I5" s="28"/>
@@ -3413,7 +3398,7 @@
       <c r="Q6" s="22"/>
       <c r="R6" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲?
+          <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
@@ -3442,60 +3427,27 @@
     </row>
     <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="26"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="26"/>
-      <c r="F8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F8" s="21"/>
       <c r="G8" s="26"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="26"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="K8" s="26"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="26"/>
-      <c r="N8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N8" s="21"/>
       <c r="O8" s="26"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="26"/>
-      <c r="R8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R8" s="21"/>
       <c r="S8" s="26"/>
     </row>
     <row r="9" ht="96.05" customHeight="true">
@@ -3572,11 +3524,7 @@
         </is>
       </c>
       <c r="I10" s="25"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ʒ</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="25"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
@@ -3584,11 +3532,7 @@
         </is>
       </c>
       <c r="M10" s="25"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ʒ</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="25"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
@@ -3623,8 +3567,7 @@
       <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="K11" s="26"/>
@@ -3644,8 +3587,7 @@
       <c r="O11" s="26"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲∼
-‹</t>
+          <t xml:space="preserve">仲∼</t>
         </is>
       </c>
       <c r="Q11" s="26"/>
@@ -3732,11 +3674,7 @@
         </is>
       </c>
       <c r="C14" s="26"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="26"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
@@ -3745,29 +3683,13 @@
         </is>
       </c>
       <c r="G14" s="26"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="26"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="26"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="26"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="26"/>
       <c r="P14" s="21"/>
       <c r="Q14" s="26"/>

--- a/sheets/조재수대금교본/검수/고姑 본청.xlsx
+++ b/sheets/조재수대금교본/검수/고姑 본청.xlsx
@@ -3239,7 +3239,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌ㄱ</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -3252,13 +3252,13 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">姑∽</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
       <c r="R3" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">姑∽</t>
         </is>
       </c>
       <c r="S3" s="24"/>
@@ -3271,13 +3271,25 @@
       <c r="E4" s="25"/>
       <c r="F4" s="21"/>
       <c r="G4" s="25"/>
-      <c r="H4" s="21"/>
+      <c r="H4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ʒ</t>
+        </is>
+      </c>
       <c r="I4" s="25"/>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ʒ</t>
+        </is>
+      </c>
       <c r="K4" s="25"/>
       <c r="L4" s="21"/>
       <c r="M4" s="25"/>
-      <c r="N4" s="21"/>
+      <c r="N4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ʒ</t>
+        </is>
+      </c>
       <c r="O4" s="25"/>
       <c r="P4" s="21"/>
       <c r="Q4" s="25"/>
@@ -3524,7 +3536,11 @@
         </is>
       </c>
       <c r="I10" s="25"/>
-      <c r="J10" s="21"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ʒ</t>
+        </is>
+      </c>
       <c r="K10" s="25"/>
       <c r="L10" s="21" t="inlineStr">
         <is>
@@ -3532,7 +3548,11 @@
         </is>
       </c>
       <c r="M10" s="25"/>
-      <c r="N10" s="21"/>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ʒ</t>
+        </is>
+      </c>
       <c r="O10" s="25"/>
       <c r="P10" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/고姑 본청.xlsx
+++ b/sheets/조재수대금교본/검수/고姑 본청.xlsx
@@ -3156,30 +3156,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="64.52" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="96.05" customHeight="true">
+    <row r="3" ht="106.4" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="S3" s="24"/>
     </row>
-    <row r="4" ht="96.05" customHeight="true">
+    <row r="4" ht="106.4" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="25"/>
@@ -3296,7 +3296,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="25"/>
     </row>
-    <row r="5" ht="96.05" customHeight="true">
+    <row r="5" ht="106.4" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="26"/>
     </row>
-    <row r="6" ht="96.05" customHeight="true">
+    <row r="6" ht="106.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="S6" s="29"/>
     </row>
-    <row r="7" ht="96.05" customHeight="true">
+    <row r="7" ht="106.4" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="25"/>
@@ -3437,7 +3437,7 @@
       <c r="R7" s="21"/>
       <c r="S7" s="25"/>
     </row>
-    <row r="8" ht="96.05" customHeight="true">
+    <row r="8" ht="106.4" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="26"/>
@@ -3462,7 +3462,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="26"/>
     </row>
-    <row r="9" ht="96.05" customHeight="true">
+    <row r="9" ht="106.4" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="96.05" customHeight="true">
+    <row r="10" ht="106.4" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="25"/>
@@ -3564,7 +3564,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="25"/>
     </row>
-    <row r="11" ht="96.05" customHeight="true">
+    <row r="11" ht="106.4" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="26"/>
@@ -3614,7 +3614,7 @@
       <c r="R11" s="21"/>
       <c r="S11" s="26"/>
     </row>
-    <row r="12" ht="96.05" customHeight="true">
+    <row r="12" ht="106.4" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="96.05" customHeight="true">
+    <row r="13" ht="106.4" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -3686,7 +3686,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="25"/>
     </row>
-    <row r="14" ht="96.05" customHeight="true">
+    <row r="14" ht="106.4" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3722,6 +3722,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>